--- a/Rutas fijas Mayo.xlsx
+++ b/Rutas fijas Mayo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\TML\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5E6CE9B3-5079-4325-BA8C-542FAC2BB7FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C901AF04-42ED-4E0E-9AFC-4B7F16529302}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{D09B0022-7EF7-407F-9BC7-0B5815E45CB7}"/>
   </bookViews>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="189">
   <si>
     <t>PAE EL SALVADOR, LTDA. DE C.V.</t>
   </si>
@@ -592,9 +592,6 @@
   </si>
   <si>
     <t>DS00IM</t>
-  </si>
-  <si>
-    <t>COORDINACION</t>
   </si>
   <si>
     <t>W00511</t>
@@ -1562,7 +1559,7 @@
         <v>14</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>15</v>
@@ -1580,10 +1577,10 @@
         <v>19</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="N1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.35">
@@ -5824,7 +5821,7 @@
         <v>6</v>
       </c>
       <c r="N102" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.35">
@@ -5841,28 +5838,28 @@
         <v>29</v>
       </c>
       <c r="E103" t="s">
+        <v>183</v>
+      </c>
+      <c r="F103">
+        <v>3</v>
+      </c>
+      <c r="G103" t="s">
         <v>184</v>
       </c>
-      <c r="F103">
-        <v>3</v>
-      </c>
-      <c r="G103" t="s">
+      <c r="H103" t="s">
+        <v>24</v>
+      </c>
+      <c r="J103" t="s">
+        <v>25</v>
+      </c>
+      <c r="K103" t="s">
+        <v>26</v>
+      </c>
+      <c r="L103" t="s">
+        <v>27</v>
+      </c>
+      <c r="M103" t="s">
         <v>185</v>
-      </c>
-      <c r="H103" t="s">
-        <v>24</v>
-      </c>
-      <c r="J103" t="s">
-        <v>25</v>
-      </c>
-      <c r="K103" t="s">
-        <v>26</v>
-      </c>
-      <c r="L103" t="s">
-        <v>27</v>
-      </c>
-      <c r="M103" t="s">
-        <v>186</v>
       </c>
       <c r="N103" t="s">
         <v>176</v>
